--- a/data/trans_camb/Q45B_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/Q45B_R-Provincia-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,87; -0,48</t>
+          <t>-6,41; -0,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 0,18</t>
+          <t>-5,7; 0,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 4,48</t>
+          <t>-4,79; 4,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,75; -0,95</t>
+          <t>-9,05; -0,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 1,33</t>
+          <t>-4,44; 1,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,03; -0,99</t>
+          <t>-6,14; -1,07</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-95,63; -1,72</t>
+          <t>-93,64; 10,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-90,58; 32,87</t>
+          <t>-88,38; 50,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-46,55; 84,37</t>
+          <t>-47,5; 87,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-84,31; -8,75</t>
+          <t>-83,96; -1,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-55,59; 31,24</t>
+          <t>-57,99; 32,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-78,41; -17,79</t>
+          <t>-80,66; -20,88</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 0,95</t>
+          <t>-1,79; 1,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,0; -0,79</t>
+          <t>-3,09; -0,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,78; -0,3</t>
+          <t>-6,11; -0,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,24; -3,89</t>
+          <t>-8,25; -3,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,32; -0,19</t>
+          <t>-3,43; -0,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,26; -2,69</t>
+          <t>-5,2; -2,74</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-75,68; 114,91</t>
+          <t>-74,62; 178,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -873,22 +873,22 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-72,86; -2,76</t>
+          <t>-73,05; -3,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-97,44; -70,02</t>
+          <t>-97,69; -71,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-65,6; -3,54</t>
+          <t>-66,42; -6,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-98,03; -74,94</t>
+          <t>-100,0; -76,93</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 1,77</t>
+          <t>-0,88; 1,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 0,93</t>
+          <t>-1,19; 0,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 2,71</t>
+          <t>-5,25; 2,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 2,11</t>
+          <t>-5,9; 1,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 1,7</t>
+          <t>-2,55; 1,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 0,91</t>
+          <t>-3,14; 1,07</t>
         </is>
       </c>
     </row>
@@ -1029,22 +1029,22 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-53,2; 46,83</t>
+          <t>-53,4; 42,67</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-57,5; 36,46</t>
+          <t>-55,74; 26,41</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-47,76; 57,46</t>
+          <t>-45,94; 48,02</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-56,03; 25,74</t>
+          <t>-55,78; 34,71</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,72; -0,43</t>
+          <t>-3,58; -0,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 0,08</t>
+          <t>-3,26; 0,21</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,22; -0,66</t>
+          <t>-7,25; -0,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,48; -2,4</t>
+          <t>-8,17; -2,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,62; -1,11</t>
+          <t>-4,59; -0,78</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,14; -1,68</t>
+          <t>-5,03; -1,5</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 111,49</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 98,23</t>
-        </is>
-      </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-74,24; -5,74</t>
+          <t>-75,28; -11,05</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-86,86; -35,42</t>
+          <t>-86,76; -34,89</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-77,67; -27,4</t>
+          <t>-78,04; -19,66</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-85,97; -39,21</t>
+          <t>-83,43; -37,52</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 0,98</t>
+          <t>-4,18; 0,83</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 1,36</t>
+          <t>-4,39; 0,93</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-9,91; -1,04</t>
+          <t>-9,94; -1,04</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-11,14; -2,83</t>
+          <t>-10,93; -2,75</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,47; -0,73</t>
+          <t>-6,19; -0,98</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,8; -1,67</t>
+          <t>-6,81; -1,68</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 248,37</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 275,99</t>
+          <t>-100,0; 144,16</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-89,13; -9,32</t>
+          <t>-89,46; -14,37</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-96,35; -50,04</t>
+          <t>-97,13; -39,69</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-87,59; -16,17</t>
+          <t>-84,86; -20,28</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-92,57; -42,46</t>
+          <t>-92,22; -38,6</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,99</t>
+          <t>0,38; 3,95</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 2,65</t>
+          <t>-0,28; 2,56</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-10,95; -1,28</t>
+          <t>-10,95; -0,96</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-15,22; -7,28</t>
+          <t>-15,34; -7,1</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 0,65</t>
+          <t>-4,72; 0,49</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-7,72; -3,15</t>
+          <t>-7,43; -3,14</t>
         </is>
       </c>
     </row>
@@ -1497,22 +1497,22 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-71,86; -9,88</t>
+          <t>-71,83; -9,13</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-97,71; -72,77</t>
+          <t>-97,95; -74,99</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-60,61; 16,16</t>
+          <t>-60,7; 13,22</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-93,71; -58,05</t>
+          <t>-94,45; -59,38</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,13; 3,21</t>
+          <t>0,15; 3,33</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 1,22</t>
+          <t>-0,89; 1,31</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 3,11</t>
+          <t>-3,15; 3,21</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-8,67; -3,47</t>
+          <t>-9,0; -3,67</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 2,75</t>
+          <t>-0,93; 2,71</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,55; -1,67</t>
+          <t>-4,66; -1,68</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-21,0; 1033,88</t>
+          <t>-19,8; 891,32</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-76,21; 455,04</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-31,44; 43,46</t>
+          <t>-29,26; 43,37</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-81,9; -47,17</t>
+          <t>-82,37; -49,4</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-19,2; 65,97</t>
+          <t>-16,07; 65,6</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-76,54; -37,49</t>
+          <t>-75,65; -37,68</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,1; 5,12</t>
+          <t>0,49; 4,94</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-3,87; -0,45</t>
+          <t>-3,88; -0,65</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2,99; 8,95</t>
+          <t>2,99; 8,88</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 2,93</t>
+          <t>-1,83; 3,16</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2,46; 6,18</t>
+          <t>2,07; 6,02</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 0,92</t>
+          <t>-2,2; 0,73</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 181,97</t>
+          <t>8,77; 189,63</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-79,25; -11,52</t>
+          <t>-78,98; -16,45</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>38,35; 176,61</t>
+          <t>38,95; 175,55</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-25,69; 56,87</t>
+          <t>-25,0; 64,23</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>40,85; 145,81</t>
+          <t>35,19; 144,45</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-37,81; 22,59</t>
+          <t>-37,61; 17,56</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 1,26</t>
+          <t>-0,26; 1,32</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-1,73; -0,51</t>
+          <t>-1,69; -0,5</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 0,89</t>
+          <t>-1,76; 0,93</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-5,34; -3,15</t>
+          <t>-5,45; -3,15</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 0,85</t>
+          <t>-0,77; 0,79</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-3,26; -1,96</t>
+          <t>-3,36; -2,01</t>
         </is>
       </c>
     </row>
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-11,05; 70,85</t>
+          <t>-11,06; 79,75</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-69,95; -27,59</t>
+          <t>-69,2; -27,51</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-21,45; 12,06</t>
+          <t>-20,42; 13,24</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-63,85; -44,43</t>
+          <t>-63,45; -43,78</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-12,77; 18,75</t>
+          <t>-14,2; 16,85</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-61,9; -44,32</t>
+          <t>-62,24; -44,25</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/Q45B_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/Q45B_R-Provincia-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,41; -0,31</t>
+          <t>-6,16; -0,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 0,35</t>
+          <t>-5,78; 0,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 4,71</t>
+          <t>-5,08; 5,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,05; -0,72</t>
+          <t>-8,82; -0,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 1,23</t>
+          <t>-4,49; 1,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,14; -1,07</t>
+          <t>-6,18; -1,28</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-93,64; 10,78</t>
+          <t>-93,89; 5,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-88,38; 50,43</t>
+          <t>-88,23; 30,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-47,5; 87,5</t>
+          <t>-50,46; 83,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-83,96; -1,26</t>
+          <t>-84,11; -5,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-57,99; 32,69</t>
+          <t>-57,69; 30,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-80,66; -20,88</t>
+          <t>-81,12; -25,85</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 1,13</t>
+          <t>-1,98; 1,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,09; -0,73</t>
+          <t>-3,16; -0,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,11; -0,61</t>
+          <t>-6,03; -0,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,25; -3,71</t>
+          <t>-8,54; -3,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,43; -0,31</t>
+          <t>-3,49; -0,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,2; -2,74</t>
+          <t>-5,23; -2,71</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-74,62; 178,74</t>
+          <t>-77,88; 158,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -873,22 +873,22 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-73,05; -3,3</t>
+          <t>-73,07; -7,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-97,69; -71,21</t>
+          <t>-97,71; -71,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-66,42; -6,38</t>
+          <t>-68,52; -7,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -76,93</t>
+          <t>-98,1; -78,15</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 1,76</t>
+          <t>-0,9; 1,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 0,65</t>
+          <t>-1,23; 0,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 2,6</t>
+          <t>-5,25; 2,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 1,71</t>
+          <t>-6,09; 1,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 1,62</t>
+          <t>-2,71; 1,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 1,07</t>
+          <t>-3,09; 0,9</t>
         </is>
       </c>
     </row>
@@ -1029,22 +1029,22 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-53,4; 42,67</t>
+          <t>-53,12; 41,25</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-55,74; 26,41</t>
+          <t>-55,89; 34,06</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-45,94; 48,02</t>
+          <t>-47,78; 42,57</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-55,78; 34,71</t>
+          <t>-56,15; 26,81</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,58; -0,31</t>
+          <t>-4,04; -0,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 0,21</t>
+          <t>-3,44; 0,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,25; -0,78</t>
+          <t>-7,35; -0,87</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,17; -2,1</t>
+          <t>-8,14; -2,01</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,59; -0,78</t>
+          <t>-4,67; -0,98</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,03; -1,5</t>
+          <t>-5,04; -1,56</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 111,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 150,68</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-75,28; -11,05</t>
+          <t>-75,8; -12,76</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-86,76; -34,89</t>
+          <t>-85,76; -32,62</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-78,04; -19,66</t>
+          <t>-77,46; -23,91</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-83,43; -37,52</t>
+          <t>-84,75; -38,63</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 0,83</t>
+          <t>-4,15; 0,86</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 0,93</t>
+          <t>-3,87; 1,34</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-9,94; -1,04</t>
+          <t>-10,03; -1,23</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-10,93; -2,75</t>
+          <t>-11,1; -2,69</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,19; -0,98</t>
+          <t>-6,27; -0,87</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,81; -1,68</t>
+          <t>-6,54; -1,57</t>
         </is>
       </c>
     </row>
@@ -1336,27 +1336,27 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 144,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-89,46; -14,37</t>
+          <t>-88,73; -4,7</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-97,13; -39,69</t>
+          <t>-100,0; -48,59</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-84,86; -20,28</t>
+          <t>-85,82; -14,0</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-92,22; -38,6</t>
+          <t>-92,46; -38,73</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,95</t>
+          <t>0,4; 4,02</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 2,56</t>
+          <t>-0,24; 2,95</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-10,95; -0,96</t>
+          <t>-10,34; -1,16</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-15,34; -7,1</t>
+          <t>-15,32; -7,53</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 0,49</t>
+          <t>-4,67; 0,73</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-7,43; -3,14</t>
+          <t>-7,66; -3,21</t>
         </is>
       </c>
     </row>
@@ -1497,22 +1497,22 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-71,83; -9,13</t>
+          <t>-71,17; -8,24</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-97,95; -74,99</t>
+          <t>-97,52; -72,42</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-60,7; 13,22</t>
+          <t>-60,71; 16,43</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-94,45; -59,38</t>
+          <t>-93,9; -60,77</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,15; 3,33</t>
+          <t>0,17; 3,46</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 1,31</t>
+          <t>-0,9; 1,33</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 3,21</t>
+          <t>-2,77; 3,56</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-9,0; -3,67</t>
+          <t>-8,85; -3,65</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 2,71</t>
+          <t>-0,89; 2,6</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,66; -1,68</t>
+          <t>-4,58; -1,54</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-19,8; 891,32</t>
+          <t>-21,63; 1106,04</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-76,21; 455,04</t>
+          <t>-81,56; 502,22</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-29,26; 43,37</t>
+          <t>-26,0; 49,33</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-82,37; -49,4</t>
+          <t>-82,07; -46,65</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-16,07; 65,6</t>
+          <t>-15,39; 62,38</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-75,65; -37,68</t>
+          <t>-76,51; -39,02</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,94</t>
+          <t>0,39; 4,75</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-3,88; -0,65</t>
+          <t>-3,72; -0,66</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2,99; 8,88</t>
+          <t>2,86; 8,86</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 3,16</t>
+          <t>-1,72; 3,03</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2,07; 6,02</t>
+          <t>2,42; 6,17</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 0,73</t>
+          <t>-2,18; 0,81</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>8,77; 189,63</t>
+          <t>6,32; 170,5</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-78,98; -16,45</t>
+          <t>-80,85; -22,38</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>38,95; 175,55</t>
+          <t>37,06; 173,99</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-25,0; 64,23</t>
+          <t>-23,68; 61,34</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>35,19; 144,45</t>
+          <t>41,32; 145,43</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-37,61; 17,56</t>
+          <t>-37,8; 19,79</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 1,32</t>
+          <t>-0,18; 1,25</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-1,69; -0,5</t>
+          <t>-1,67; -0,52</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 0,93</t>
+          <t>-1,63; 0,88</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-5,45; -3,15</t>
+          <t>-5,3; -3,3</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 0,79</t>
+          <t>-0,81; 0,77</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-3,36; -2,01</t>
+          <t>-3,36; -2,06</t>
         </is>
       </c>
     </row>
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-11,06; 79,75</t>
+          <t>-8,07; 74,54</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-69,2; -27,51</t>
+          <t>-69,15; -30,29</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-20,42; 13,24</t>
+          <t>-19,29; 12,49</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-63,45; -43,78</t>
+          <t>-62,81; -45,11</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-14,2; 16,85</t>
+          <t>-14,77; 16,69</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-62,24; -44,25</t>
+          <t>-62,65; -45,22</t>
         </is>
       </c>
     </row>
